--- a/output/pdf_financials_xlsx/POOL.xlsx
+++ b/output/pdf_financials_xlsx/POOL.xlsx
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.037</v>
+        <v>-0.037</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.06601600000000001</v>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.037</v>
+        <v>-0.037</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.06601600000000001</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.037</v>
+        <v>-0.037</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.06601600000000001</v>
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>1.233333</v>
+        <v>-1.233333</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>2.200533</v>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.037</v>
+        <v>-0.037</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.06601600000000001</v>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.037</v>
+        <v>-0.037</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.06601600000000001</v>
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -5884,49 +5884,49 @@
         <v>0.0387</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.0387</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.0412</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.200142</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.308106</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.334928</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.337782</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.337782</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.393365</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.486126</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.54157</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.54157</v>
       </c>
     </row>
     <row r="93">
@@ -10198,7 +10198,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -15992,7 +15996,11 @@
           <t>Reserves (note 6)</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -17095,7 +17103,11 @@
           <t>Reserves (note 6)</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -18196,7 +18208,11 @@
           <t>Reserves (note 5) 38,700</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -35611,7 +35627,7 @@
         </is>
       </c>
       <c r="E276" s="5" t="n">
-        <v>0.037</v>
+        <v>-0.037</v>
       </c>
       <c r="F276" s="5" t="n">
         <v>-0.06601600000000001</v>

--- a/output/pdf_financials_xlsx/POOL.xlsx
+++ b/output/pdf_financials_xlsx/POOL.xlsx
@@ -2394,16 +2394,16 @@
         <v>0.006577</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.284278</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.284991</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.003319</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.010751</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.06800299999999999</v>
@@ -2510,16 +2510,16 @@
         <v>0.006577</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.284278</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.284991</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.003319</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.010751</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0.06800299999999999</v>
@@ -3206,16 +3206,16 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.284278</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.284991</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.010751</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.00106</v>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -15689,7 +15689,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -16398,7 +16398,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">

--- a/output/pdf_financials_xlsx/POOL.xlsx
+++ b/output/pdf_financials_xlsx/POOL.xlsx
@@ -4370,16 +4370,16 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.0065</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.066216</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0.133892</v>
@@ -4388,31 +4388,31 @@
         <v>0.271575</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.01775</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.102895</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.11164</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.09984800000000001</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.104888</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.216259</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.070509</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.134382</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.151279</v>
       </c>
     </row>
     <row r="68">
@@ -4446,31 +4446,31 @@
         <v>0.271575</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0</v>
+        <v>0.01775</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0</v>
+        <v>0.102895</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0</v>
+        <v>0.11164</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0</v>
+        <v>0.09984800000000001</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0</v>
+        <v>0.104888</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0</v>
+        <v>0.216259</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>0</v>
+        <v>0.070509</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>0</v>
+        <v>0.134382</v>
       </c>
       <c r="R68" s="3" t="n">
-        <v>0</v>
+        <v>0.151279</v>
       </c>
     </row>
     <row r="69">
@@ -4852,31 +4852,31 @@
         <v>0</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.200086</v>
+        <v>0.182336</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.184751</v>
+        <v>0.081856</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.711925</v>
+        <v>0.600285</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.83269</v>
+        <v>0.732842</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>1.293727</v>
+        <v>1.188839</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.381879</v>
+        <v>0.16562</v>
       </c>
       <c r="P75" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>2.695944</v>
+        <v>2.561562</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>2.081845</v>
+        <v>1.930566</v>
       </c>
     </row>
     <row r="76">
@@ -6380,13 +6380,13 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003291</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.009742000000000001</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.013033</v>
       </c>
       <c r="F101" s="3" t="n">
         <v>-0.003475</v>
@@ -6673,10 +6673,10 @@
         <v>-0.069505</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.01522</v>
+        <v>0.005478</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.036652</v>
+        <v>0.049685</v>
       </c>
       <c r="F106" s="3" t="n">
         <v>-0.027284</v>
@@ -6978,16 +6978,16 @@
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.103051</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.019149</v>
       </c>
       <c r="K111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001532</v>
       </c>
       <c r="M111" s="3" t="n">
         <v>0</v>
@@ -8364,16 +8364,16 @@
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.103051</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.019149</v>
       </c>
       <c r="K134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001532</v>
       </c>
       <c r="M134" s="3" t="n">
         <v>0</v>
@@ -8436,16 +8436,16 @@
         </is>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-0.07448399999999999</v>
+        <v>-0.177535</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-0.791225</v>
+        <v>-0.810374</v>
       </c>
       <c r="K135" s="3" t="n">
         <v>-0.566293</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-0.286087</v>
+        <v>-0.287619</v>
       </c>
       <c r="M135" s="3" t="n">
         <v>-0.375507</v>
@@ -25897,7 +25897,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -30024,7 +30028,11 @@
           <t>Net Income (loss) $</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -31618,7 +31626,11 @@
           <t>HST recoverable</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -32434,7 +32446,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
